--- a/hall/resources/sample/SeasonMatch.xlsx
+++ b/hall/resources/sample/SeasonMatch.xlsx
@@ -350,12 +350,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1493,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>

--- a/hall/resources/sample/SeasonMatch.xlsx
+++ b/hall/resources/sample/SeasonMatch.xlsx
@@ -350,12 +350,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1493,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="D5" s="1">
         <v>-1</v>
@@ -1528,7 +1528,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="D6" s="1">
         <v>-1</v>
@@ -1563,7 +1563,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="D7" s="1">
         <v>-1</v>
@@ -1598,7 +1598,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="1">
-        <v>400</v>
+        <v>1800</v>
       </c>
       <c r="D8" s="1">
         <v>-1</v>
@@ -1633,7 +1633,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>400</v>
+        <v>2400</v>
       </c>
       <c r="D9" s="1">
         <v>-1</v>
@@ -1668,7 +1668,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="1">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="D10" s="1">
         <v>-1</v>
@@ -1703,7 +1703,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="1">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="D11" s="1">
         <v>-1</v>
@@ -1738,7 +1738,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="1">
-        <v>800</v>
+        <v>3000</v>
       </c>
       <c r="D12" s="1">
         <v>-1</v>
@@ -1773,7 +1773,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="1">
-        <v>800</v>
+        <v>3600</v>
       </c>
       <c r="D13" s="1">
         <v>-1</v>
@@ -1808,7 +1808,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="1">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="D14" s="1">
         <v>-1</v>
@@ -1843,7 +1843,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="1">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="D15" s="1">
         <v>-1</v>
@@ -1878,7 +1878,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="1">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="D16" s="1">
         <v>-1</v>
@@ -1913,7 +1913,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="1">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="D17" s="1">
         <v>-1</v>
@@ -1948,7 +1948,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="1">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="D18" s="1">
         <v>-1</v>
